--- a/sample_data.xlsx
+++ b/sample_data.xlsx
@@ -1,43 +1,460 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason\Projects\load_configurator_app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEDAA37-146F-4FA3-A823-4BE832B28CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-43476" yWindow="1188" windowWidth="17280" windowHeight="8880" xr2:uid="{A1139CED-2EED-461D-8A45-C2AEED3E8BCB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="sample_data1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="28">
+  <si>
+    <t>LENGTH</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>WIDTH</t>
+  </si>
+  <si>
+    <t>HEIGHT</t>
+  </si>
+  <si>
+    <t>MASS</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>GEN-001</t>
+  </si>
+  <si>
+    <t>CONSIGNMENT</t>
+  </si>
+  <si>
+    <t>GEN-002</t>
+  </si>
+  <si>
+    <t>GEN-003</t>
+  </si>
+  <si>
+    <t>DE88GC</t>
+  </si>
+  <si>
+    <t>DE150GC</t>
+  </si>
+  <si>
+    <t>DE110E2</t>
+  </si>
+  <si>
+    <t>DE110GC</t>
+  </si>
+  <si>
+    <t>DE220GC</t>
+  </si>
+  <si>
+    <t>DE400GC</t>
+  </si>
+  <si>
+    <t>DE65GC</t>
+  </si>
+  <si>
+    <t>DE450E0</t>
+  </si>
+  <si>
+    <t>DE850E0</t>
+  </si>
+  <si>
+    <t>DE500GC</t>
+  </si>
+  <si>
+    <t>DE50GC</t>
+  </si>
+  <si>
+    <t>DE33GC</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -45,15 +462,564 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="34" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="34" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="35" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="35" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="35" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="35" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="35" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="35" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="35" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -79,39 +1045,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -144,9 +1110,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -179,6 +1162,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -240,13 +1240,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -255,6 +1248,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -319,21 +1319,666 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F99A702-F2DD-4857-BE6B-40AE175852D3}">
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="39.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1.62</v>
+      </c>
+      <c r="E5" s="9">
+        <v>1.3580000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="6">
+        <v>3.38</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1.85</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1.881</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="7">
+        <v>2.77</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1.63</v>
+      </c>
+      <c r="E7" s="11">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1.68</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1.196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.68</v>
+      </c>
+      <c r="E9" s="12">
+        <v>1.196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="6">
+        <v>3.38</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1.85</v>
+      </c>
+      <c r="E10" s="10">
+        <v>1.881</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="5">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1.62</v>
+      </c>
+      <c r="E11" s="13">
+        <v>1.3580000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="6">
+        <v>3.38</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1.85</v>
+      </c>
+      <c r="E12" s="14">
+        <v>1.881</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="7">
+        <v>2.77</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1.63</v>
+      </c>
+      <c r="E13" s="15">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="C14" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="D14" s="8">
+        <v>1.68</v>
+      </c>
+      <c r="E14" s="16">
+        <v>1.196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="C15" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1.68</v>
+      </c>
+      <c r="E15" s="16">
+        <v>1.196</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="6">
+        <v>3.38</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1.85</v>
+      </c>
+      <c r="E16" s="14">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="18">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C17" s="18">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="D17" s="18">
+        <v>1.62</v>
+      </c>
+      <c r="E17" s="19">
+        <v>1.3580000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="21">
+        <v>3.38</v>
+      </c>
+      <c r="C18" s="21">
+        <v>1.17</v>
+      </c>
+      <c r="D18" s="21">
+        <v>1.85</v>
+      </c>
+      <c r="E18" s="22">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="24">
+        <v>4</v>
+      </c>
+      <c r="C19" s="24">
+        <v>1.46</v>
+      </c>
+      <c r="D19" s="24">
+        <v>2.12</v>
+      </c>
+      <c r="E19" s="25">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="27">
+        <v>0.96</v>
+      </c>
+      <c r="C20" s="27">
+        <v>2.33</v>
+      </c>
+      <c r="D20" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="E20" s="28">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="27">
+        <v>0.96</v>
+      </c>
+      <c r="C21" s="27">
+        <v>2.33</v>
+      </c>
+      <c r="D21" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="E21" s="28">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="27">
+        <v>0.96</v>
+      </c>
+      <c r="C22" s="27">
+        <v>2.33</v>
+      </c>
+      <c r="D22" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="E22" s="28">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="27">
+        <v>0.96</v>
+      </c>
+      <c r="C23" s="27">
+        <v>2.33</v>
+      </c>
+      <c r="D23" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="E23" s="28">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="21">
+        <v>4.93</v>
+      </c>
+      <c r="C24" s="21">
+        <v>1.66</v>
+      </c>
+      <c r="D24" s="21">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="E24" s="22">
+        <v>4.7069999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="18">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C25" s="18">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="D25" s="18">
+        <v>1.62</v>
+      </c>
+      <c r="E25" s="19">
+        <v>1.3580000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="21">
+        <v>3.38</v>
+      </c>
+      <c r="C26" s="21">
+        <v>1.17</v>
+      </c>
+      <c r="D26" s="21">
+        <v>1.85</v>
+      </c>
+      <c r="E26" s="22">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="30">
+        <v>5.5720000000000001</v>
+      </c>
+      <c r="C27" s="30">
+        <v>2.17</v>
+      </c>
+      <c r="D27" s="30">
+        <v>2.3980000000000001</v>
+      </c>
+      <c r="E27" s="31">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="33">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="C28" s="33">
+        <v>1.63</v>
+      </c>
+      <c r="D28" s="33">
+        <v>2.36</v>
+      </c>
+      <c r="E28" s="34">
+        <v>3.8079999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="35"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="37"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="36">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="C30" s="36">
+        <v>1.63</v>
+      </c>
+      <c r="D30" s="36">
+        <v>2.36</v>
+      </c>
+      <c r="E30" s="37">
+        <v>3.8079999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="37"/>
+    </row>
+    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="39">
+        <v>2.33</v>
+      </c>
+      <c r="C32" s="39">
+        <v>0.96</v>
+      </c>
+      <c r="D32" s="39">
+        <v>1.5</v>
+      </c>
+      <c r="E32" s="40">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="42">
+        <v>2</v>
+      </c>
+      <c r="C33" s="42">
+        <v>0.92</v>
+      </c>
+      <c r="D33" s="42">
+        <v>1.44</v>
+      </c>
+      <c r="E33" s="43">
+        <v>0.83799999999999997</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" s="45">
+        <v>2</v>
+      </c>
+      <c r="C34" s="45">
+        <v>0.92</v>
+      </c>
+      <c r="D34" s="45">
+        <v>1.44</v>
+      </c>
+      <c r="E34" s="46">
+        <v>0.83799999999999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="45">
+        <v>2</v>
+      </c>
+      <c r="C35" s="45">
+        <v>0.92</v>
+      </c>
+      <c r="D35" s="45">
+        <v>1.44</v>
+      </c>
+      <c r="E35" s="46">
+        <v>0.83799999999999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" s="45">
+        <v>2</v>
+      </c>
+      <c r="C36" s="45">
+        <v>0.92</v>
+      </c>
+      <c r="D36" s="45">
+        <v>1.44</v>
+      </c>
+      <c r="E36" s="46">
+        <v>0.83799999999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="39">
+        <v>2.33</v>
+      </c>
+      <c r="C37" s="39">
+        <v>0.96</v>
+      </c>
+      <c r="D37" s="39">
+        <v>1.5</v>
+      </c>
+      <c r="E37" s="40">
+        <v>0.877</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/sample_data.xlsx
+++ b/sample_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason\Projects\load_configurator_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEDAA37-146F-4FA3-A823-4BE832B28CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDED954-948E-4AA4-819F-346961E26BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-43476" yWindow="1188" windowWidth="17280" windowHeight="8880" xr2:uid="{A1139CED-2EED-461D-8A45-C2AEED3E8BCB}"/>
+    <workbookView xWindow="-46188" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A1139CED-2EED-461D-8A45-C2AEED3E8BCB}"/>
   </bookViews>
   <sheets>
     <sheet name="sample_data1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="32">
   <si>
     <t>LENGTH</t>
   </si>
@@ -104,6 +104,18 @@
   </si>
   <si>
     <t>DE33GC</t>
+  </si>
+  <si>
+    <t>DE250E0</t>
+  </si>
+  <si>
+    <t>DE660E0</t>
+  </si>
+  <si>
+    <t>DE16E0</t>
+  </si>
+  <si>
+    <t>DE330E0</t>
   </si>
 </sst>
 </file>
@@ -255,7 +267,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -441,20 +453,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="26">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -606,19 +606,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -658,135 +645,10 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -836,7 +698,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -847,134 +709,29 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="33" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="33" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="33" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="33" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="33" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="33" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="34" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="34" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="35" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="35" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="35" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="35" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="35" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="35" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1351,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F99A702-F2DD-4857-BE6B-40AE175852D3}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.88671875" bestFit="1" customWidth="1"/>
@@ -1408,7 +1165,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1426,559 +1183,856 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>1.1200000000000001</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>1.62</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="5">
         <v>1.3580000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="6">
-        <v>3.38</v>
-      </c>
-      <c r="C6" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1.85</v>
-      </c>
-      <c r="E6" s="10">
-        <v>1.881</v>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1.62</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1.3580000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1.62</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1.3580000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1.62</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1.3580000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B9" s="4">
         <v>2.77</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C9" s="4">
         <v>1.1200000000000001</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D9" s="4">
         <v>1.63</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E9" s="5">
         <v>1.51</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2.77</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1.63</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B11" s="4">
         <v>2.8</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C11" s="4">
         <v>1.05</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D11" s="4">
         <v>1.68</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E11" s="5">
         <v>1.196</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B12" s="4">
         <v>2.8</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C12" s="4">
         <v>1.05</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D12" s="4">
         <v>1.68</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E12" s="5">
         <v>1.196</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="6">
-        <v>3.38</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1.85</v>
-      </c>
-      <c r="E10" s="10">
-        <v>1.881</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="5">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C11" s="5">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1.62</v>
-      </c>
-      <c r="E11" s="13">
-        <v>1.3580000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="6">
-        <v>3.38</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1.85</v>
-      </c>
-      <c r="E12" s="14">
-        <v>1.881</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="7">
-        <v>2.77</v>
-      </c>
-      <c r="C13" s="7">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="D13" s="7">
+        <v>19</v>
+      </c>
+      <c r="B13" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1.05</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1.68</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1.196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1.05</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1.68</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1.196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="4">
+        <v>3.38</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1.17</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1.881</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="4">
+        <v>3.38</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1.17</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1.881</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="4">
+        <v>3.38</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1.17</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1.881</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="4">
+        <v>2.6619999999999999</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1.1120000000000001</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1.766</v>
+      </c>
+      <c r="E18" s="5">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="4">
+        <v>2.6619999999999999</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1.1120000000000001</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1.766</v>
+      </c>
+      <c r="E19" s="5">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="4">
+        <v>3.38</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1.17</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="E20" s="5">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4">
+        <v>3.38</v>
+      </c>
+      <c r="C21" s="4">
+        <v>1.17</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4">
+        <v>3.38</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1.17</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="4">
+        <v>3.38</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1.17</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="4">
+        <v>4.03</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1.46</v>
+      </c>
+      <c r="D24" s="4">
+        <v>2.19</v>
+      </c>
+      <c r="E24" s="5">
+        <v>2.782</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="4">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="C25" s="4">
         <v>1.63</v>
       </c>
-      <c r="E13" s="15">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="8">
-        <v>2.8</v>
-      </c>
-      <c r="C14" s="8">
-        <v>1.05</v>
-      </c>
-      <c r="D14" s="8">
-        <v>1.68</v>
-      </c>
-      <c r="E14" s="16">
-        <v>1.196</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="8">
-        <v>2.8</v>
-      </c>
-      <c r="C15" s="8">
-        <v>1.05</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1.68</v>
-      </c>
-      <c r="E15" s="16">
-        <v>1.196</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="6">
-        <v>3.38</v>
-      </c>
-      <c r="C16" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="D16" s="6">
-        <v>1.85</v>
-      </c>
-      <c r="E16" s="14">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="18">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C17" s="18">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="D17" s="18">
-        <v>1.62</v>
-      </c>
-      <c r="E17" s="19">
-        <v>1.3580000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="21">
-        <v>3.38</v>
-      </c>
-      <c r="C18" s="21">
-        <v>1.17</v>
-      </c>
-      <c r="D18" s="21">
-        <v>1.85</v>
-      </c>
-      <c r="E18" s="22">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="24">
-        <v>4</v>
-      </c>
-      <c r="C19" s="24">
+      <c r="D25" s="4">
+        <v>2.36</v>
+      </c>
+      <c r="E25" s="5">
+        <v>3.8079999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1.63</v>
+      </c>
+      <c r="D26" s="4">
+        <v>2.36</v>
+      </c>
+      <c r="E26" s="5">
+        <v>3.8079999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="4">
+        <v>2.33</v>
+      </c>
+      <c r="C27" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="4">
+        <v>2.33</v>
+      </c>
+      <c r="C28" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="4">
+        <v>2.33</v>
+      </c>
+      <c r="C29" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="4">
+        <v>2.33</v>
+      </c>
+      <c r="C30" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="4">
+        <v>5.5720000000000001</v>
+      </c>
+      <c r="C31" s="6">
+        <v>2.17</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2.3980000000000001</v>
+      </c>
+      <c r="E31" s="5">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="7">
+        <v>5.5720000000000001</v>
+      </c>
+      <c r="C32" s="8">
+        <v>2.17</v>
+      </c>
+      <c r="D32" s="7">
+        <v>2.3980000000000001</v>
+      </c>
+      <c r="E32" s="9">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4">
+        <v>5.32</v>
+      </c>
+      <c r="C33" s="4">
+        <v>1.92</v>
+      </c>
+      <c r="D33" s="4">
+        <v>2.29</v>
+      </c>
+      <c r="E33" s="5">
+        <v>5.952</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" s="10">
+        <v>2</v>
+      </c>
+      <c r="C34" s="10">
+        <v>0.92</v>
+      </c>
+      <c r="D34" s="10">
+        <v>1.44</v>
+      </c>
+      <c r="E34" s="11">
+        <v>0.83799999999999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="4">
+        <v>2</v>
+      </c>
+      <c r="C35" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1.44</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0.83799999999999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" s="4">
+        <v>2</v>
+      </c>
+      <c r="C36" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1.44</v>
+      </c>
+      <c r="E36" s="5">
+        <v>0.83799999999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" s="4">
+        <v>2</v>
+      </c>
+      <c r="C37" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1.44</v>
+      </c>
+      <c r="E37" s="5">
+        <v>0.83799999999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" s="4">
+        <v>2</v>
+      </c>
+      <c r="C38" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1.44</v>
+      </c>
+      <c r="E38" s="5">
+        <v>0.83799999999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="4">
+        <v>4.93</v>
+      </c>
+      <c r="C39" s="4">
+        <v>1.66</v>
+      </c>
+      <c r="D39" s="4">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="E39" s="5">
+        <v>4.7069999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" s="4">
+        <v>2</v>
+      </c>
+      <c r="C40" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="D40" s="4">
+        <v>1.44</v>
+      </c>
+      <c r="E40" s="5">
+        <v>0.83699999999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="C41" s="4">
+        <v>0.62</v>
+      </c>
+      <c r="D41" s="4">
+        <v>1.115</v>
+      </c>
+      <c r="E41" s="5">
+        <v>0.44700000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="C42" s="4">
+        <v>0.62</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1.115</v>
+      </c>
+      <c r="E42" s="5">
+        <v>0.44700000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" s="4">
+        <v>2.33</v>
+      </c>
+      <c r="C43" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="D43" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E43" s="5">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" s="4">
+        <v>2.33</v>
+      </c>
+      <c r="C44" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="D44" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E44" s="5">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" s="4">
+        <v>2.33</v>
+      </c>
+      <c r="C45" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E45" s="5">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="4">
+        <v>4.03</v>
+      </c>
+      <c r="C46" s="4">
         <v>1.46</v>
       </c>
-      <c r="D19" s="24">
-        <v>2.12</v>
-      </c>
-      <c r="E19" s="25">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="26" t="s">
+      <c r="D46" s="4">
+        <v>2.19</v>
+      </c>
+      <c r="E46" s="5">
+        <v>2.782</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="4">
+        <v>3.988</v>
+      </c>
+      <c r="C47" s="4">
+        <v>1.2070000000000001</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1.867</v>
+      </c>
+      <c r="E47" s="5">
+        <v>2.8540000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" s="4">
+        <v>4.93</v>
+      </c>
+      <c r="C48" s="4">
+        <v>1.66</v>
+      </c>
+      <c r="D48" s="4">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="E48" s="5">
+        <v>4.7069999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49" s="4">
+        <v>4.93</v>
+      </c>
+      <c r="C49" s="4">
+        <v>1.66</v>
+      </c>
+      <c r="D49" s="4">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="E49" s="5">
+        <v>4.7069999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="4">
+        <v>2.33</v>
+      </c>
+      <c r="C50" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="D50" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E50" s="5">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B51" s="4">
+        <v>2.33</v>
+      </c>
+      <c r="C51" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E51" s="5">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" s="4">
+        <v>2.33</v>
+      </c>
+      <c r="C52" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="D52" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E52" s="5">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B53" s="4">
+        <v>2.33</v>
+      </c>
+      <c r="C53" s="4">
         <v>0.96</v>
       </c>
-      <c r="C20" s="27">
+      <c r="D53" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E53" s="5">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="4">
         <v>2.33</v>
       </c>
-      <c r="D20" s="27">
+      <c r="C54" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="D54" s="4">
         <v>1.5</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E54" s="5">
         <v>0.98</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="27">
-        <v>0.96</v>
-      </c>
-      <c r="C21" s="27">
-        <v>2.33</v>
-      </c>
-      <c r="D21" s="27">
-        <v>1.5</v>
-      </c>
-      <c r="E21" s="28">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="27">
-        <v>0.96</v>
-      </c>
-      <c r="C22" s="27">
-        <v>2.33</v>
-      </c>
-      <c r="D22" s="27">
-        <v>1.5</v>
-      </c>
-      <c r="E22" s="28">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="27">
-        <v>0.96</v>
-      </c>
-      <c r="C23" s="27">
-        <v>2.33</v>
-      </c>
-      <c r="D23" s="27">
-        <v>1.5</v>
-      </c>
-      <c r="E23" s="28">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="21">
-        <v>4.93</v>
-      </c>
-      <c r="C24" s="21">
-        <v>1.66</v>
-      </c>
-      <c r="D24" s="21">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="E24" s="22">
-        <v>4.7069999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="18">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C25" s="18">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="D25" s="18">
-        <v>1.62</v>
-      </c>
-      <c r="E25" s="19">
-        <v>1.3580000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="21">
-        <v>3.38</v>
-      </c>
-      <c r="C26" s="21">
-        <v>1.17</v>
-      </c>
-      <c r="D26" s="21">
-        <v>1.85</v>
-      </c>
-      <c r="E26" s="22">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="30">
-        <v>5.5720000000000001</v>
-      </c>
-      <c r="C27" s="30">
-        <v>2.17</v>
-      </c>
-      <c r="D27" s="30">
-        <v>2.3980000000000001</v>
-      </c>
-      <c r="E27" s="31">
-        <v>6.69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="33">
-        <v>4.7699999999999996</v>
-      </c>
-      <c r="C28" s="33">
-        <v>1.63</v>
-      </c>
-      <c r="D28" s="33">
-        <v>2.36</v>
-      </c>
-      <c r="E28" s="34">
-        <v>3.8079999999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="35"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="37"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="36">
-        <v>4.7699999999999996</v>
-      </c>
-      <c r="C30" s="36">
-        <v>1.63</v>
-      </c>
-      <c r="D30" s="36">
-        <v>2.36</v>
-      </c>
-      <c r="E30" s="37">
-        <v>3.8079999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="35"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="37"/>
-    </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="39">
-        <v>2.33</v>
-      </c>
-      <c r="C32" s="39">
-        <v>0.96</v>
-      </c>
-      <c r="D32" s="39">
-        <v>1.5</v>
-      </c>
-      <c r="E32" s="40">
-        <v>0.877</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" s="42">
-        <v>2</v>
-      </c>
-      <c r="C33" s="42">
-        <v>0.92</v>
-      </c>
-      <c r="D33" s="42">
-        <v>1.44</v>
-      </c>
-      <c r="E33" s="43">
-        <v>0.83799999999999997</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="45">
-        <v>2</v>
-      </c>
-      <c r="C34" s="45">
-        <v>0.92</v>
-      </c>
-      <c r="D34" s="45">
-        <v>1.44</v>
-      </c>
-      <c r="E34" s="46">
-        <v>0.83799999999999997</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" s="45">
-        <v>2</v>
-      </c>
-      <c r="C35" s="45">
-        <v>0.92</v>
-      </c>
-      <c r="D35" s="45">
-        <v>1.44</v>
-      </c>
-      <c r="E35" s="46">
-        <v>0.83799999999999997</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="B36" s="45">
-        <v>2</v>
-      </c>
-      <c r="C36" s="45">
-        <v>0.92</v>
-      </c>
-      <c r="D36" s="45">
-        <v>1.44</v>
-      </c>
-      <c r="E36" s="46">
-        <v>0.83799999999999997</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="39">
-        <v>2.33</v>
-      </c>
-      <c r="C37" s="39">
-        <v>0.96</v>
-      </c>
-      <c r="D37" s="39">
-        <v>1.5</v>
-      </c>
-      <c r="E37" s="40">
-        <v>0.877</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>